--- a/Evaluation/score_eval/prone_score_GT.xlsx
+++ b/Evaluation/score_eval/prone_score_GT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dvirbuss\PycharmProjects\infant-analyzer-app\Evaluation\score_eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8E174F3-DD85-4B72-90A4-EC7D3096F785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7989FDC5-806F-4AD5-AC4E-DD0F8C1CE0BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5385" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>video_name</t>
   </si>
@@ -120,6 +120,36 @@
   </si>
   <si>
     <t>prone_video_16</t>
+  </si>
+  <si>
+    <t>prone_video_10</t>
+  </si>
+  <si>
+    <t>prone_video_01</t>
+  </si>
+  <si>
+    <t>prone_video_02</t>
+  </si>
+  <si>
+    <t>prone_video_03</t>
+  </si>
+  <si>
+    <t>prone_video_04</t>
+  </si>
+  <si>
+    <t>prone_video_05</t>
+  </si>
+  <si>
+    <t>prone_video_06</t>
+  </si>
+  <si>
+    <t>prone_video_07</t>
+  </si>
+  <si>
+    <t>prone_video_08</t>
+  </si>
+  <si>
+    <t>prone_video_09</t>
   </si>
 </sst>
 </file>
@@ -143,7 +173,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -153,6 +183,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -184,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -195,6 +231,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -475,7 +515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr defaultColWidth="15.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="15.42578125" style="2"/>
@@ -550,33 +590,17 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
+      <c r="A2" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
@@ -592,33 +616,17 @@
       <c r="V2" s="3"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>1</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
+      <c r="A3" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -634,11 +642,11 @@
       <c r="V3" s="3"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+      <c r="A4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -660,11 +668,11 @@
       <c r="V4" s="3"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -686,11 +694,11 @@
       <c r="V5" s="3"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -711,6 +719,266 @@
       <c r="U6" s="3"/>
       <c r="V6" s="3"/>
     </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3"/>
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3"/>
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3"/>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3"/>
+      <c r="R12" s="3"/>
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3"/>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3"/>
+      <c r="R13" s="3"/>
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3"/>
+      <c r="O14" s="3"/>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3"/>
+      <c r="R14" s="3"/>
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+      <c r="U14" s="3"/>
+      <c r="V14" s="3"/>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3"/>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3"/>
+      <c r="R15" s="3"/>
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3"/>
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
